--- a/rules/CORE-000737/positive/01/data/CORE-000737-positive-01.xlsx
+++ b/rules/CORE-000737/positive/01/data/CORE-000737-positive-01.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FDATCHSP</t>
+          <t>HLTSUBJI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FDA Technical Specification</t>
+          <t>Healthy Subject Indicator</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HLTSUBJI</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Healthy Subject Indicator</t>
+          <t>Trial Length</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P24W</t>
         </is>
       </c>
     </row>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>NARMS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trial Length</t>
+          <t>Planned Number of Arms</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>P24W</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1100,17 +1100,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NARMS</t>
+          <t>NCOHORT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Planned Number of Arms</t>
+          <t>Number of Groups/Cohorts</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NCOHORT</t>
+          <t>OBJPRIM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Number of Groups/Cohorts</t>
+          <t>Trial Primary Objective</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Evaluate efficacy</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OBJPRIM</t>
+          <t>OBJSEC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trial Primary Objective</t>
+          <t>Trial Secondary Objective</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Evaluate efficacy</t>
+          <t>Evaluate safety</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OBJSEC</t>
+          <t>ONGOSIND</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trial Secondary Objective</t>
+          <t>Ongoing Study Indicator</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Evaluate safety</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ONGOSIND</t>
+          <t>OUTMSPRI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ongoing Study Indicator</t>
+          <t>Primary Outcome Measure</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADAS-Cog change from baseline</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OUTMSPRI</t>
+          <t>PDPSTIND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Primary Outcome Measure</t>
+          <t>Pediatric Postmarket Study Indicator</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ADAS-Cog change from baseline</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PDPSTIND</t>
+          <t>PDSTIND</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pediatric Postmarket Study Indicator</t>
+          <t>Pediatric Study Indicator</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PDSTIND</t>
+          <t>PIPIND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pediatric Study Indicator</t>
+          <t>Pediatric Investigation Plan Indicator</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PIPIND</t>
+          <t>PLANSUB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pediatric Investigation Plan Indicator</t>
+          <t>Planned Number of Subjects</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PLANSUB</t>
+          <t>RDIND</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Planned Number of Subjects</t>
+          <t>Rare Disease Indicator</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1400,17 +1400,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDIND</t>
+          <t>REGID</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rare Disease Indicator</t>
+          <t>Registry Identifier</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>NCT00000000</t>
         </is>
       </c>
     </row>
@@ -1430,17 +1430,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>REGID</t>
+          <t>SENDTC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Registry Identifier</t>
+          <t>Study End Date</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NCT00000000</t>
+          <t>2024-12-31</t>
         </is>
       </c>
     </row>
@@ -1460,17 +1460,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SENDTC</t>
+          <t>SEXPOP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Study End Date</t>
+          <t>Sex of Participants</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>BOTH</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SEXPOP</t>
+          <t>SPONSOR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sex of Participants</t>
+          <t>Clinical Study Sponsor</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>CDISC</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SPONSOR</t>
+          <t>SDTMVER</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Clinical Study Sponsor</t>
+          <t>SDTM Version</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>CDISC</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SDTMVER</t>
+          <t>SDTIGVER</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SDTM Version</t>
+          <t>SDTM IG Version</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.4</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SDTIGVER</t>
+          <t>STYPE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SDTM IG Version</t>
+          <t>Study Type</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>INTERVENTIONAL</t>
         </is>
       </c>
     </row>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>STYPE</t>
+          <t>STOPRULE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Study Type</t>
+          <t>Study Stop Rules</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INTERVENTIONAL</t>
+          <t>NONE</t>
         </is>
       </c>
     </row>
@@ -1640,17 +1640,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>STOPRULE</t>
+          <t>SSTDTC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Study Stop Rules</t>
+          <t>Study Start Date</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>2024-01-01</t>
         </is>
       </c>
     </row>
@@ -1670,17 +1670,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSTDTC</t>
+          <t>TBLIND</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Study Start Date</t>
+          <t>Trial Blinding Schema</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>DOUBLE BLIND</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TBLIND</t>
+          <t>TCNTRL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trial Blinding Schema</t>
+          <t>Control Type</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DOUBLE BLIND</t>
+          <t>PLACEBO</t>
         </is>
       </c>
     </row>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>TCNTRL</t>
+          <t>THERAREA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Control Type</t>
+          <t>Therapeutic Area</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>PLACEBO</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>THERAREA</t>
+          <t>TITLE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Therapeutic Area</t>
+          <t>Trial Title</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>Safety and Efficacy Pilot Study</t>
         </is>
       </c>
     </row>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TITLE</t>
+          <t>TPHASE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trial Title</t>
+          <t>Trial Phase Classification</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Safety and Efficacy Pilot Study</t>
+          <t>PHASE II TRIAL</t>
         </is>
       </c>
     </row>
@@ -1820,17 +1820,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TPHASE</t>
+          <t>TTYPE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trial Phase Classification</t>
+          <t>Trial Type</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>PHASE II TRIAL</t>
+          <t>EFFICACY</t>
         </is>
       </c>
     </row>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TTYPE</t>
+          <t>INDIC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trial Type</t>
+          <t>Trial Disease/Condition Indication</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>EFFICACY</t>
+          <t>Alzheimer's Disease</t>
         </is>
       </c>
     </row>
@@ -1876,21 +1876,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>INDIC</t>
+          <t>FCNTRY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trial Disease/Condition Indication</t>
+          <t>Planned Country of Investigational Sites</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease</t>
+          <t>CAN</t>
         </is>
       </c>
     </row>
@@ -1910,47 +1910,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SPREFID</t>
+          <t>RANDQT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sponsor's Study Reference ID</t>
+          <t>Randomization Quotient</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>CDISCPILOT01</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>TS</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>FCNTRY</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Planned Country of Investigational Sites</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>CAN</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>

--- a/rules/CORE-000737/positive/01/data/CORE-000737-positive-01.xlsx
+++ b/rules/CORE-000737/positive/01/data/CORE-000737-positive-01.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1010,17 +1010,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HLTSUBJI</t>
+          <t>FDATCHSP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Healthy Subject Indicator</t>
+          <t>FDA Technical Specification</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LENGTH</t>
+          <t>HLTSUBJI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trial Length</t>
+          <t>Healthy Subject Indicator</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>P24W</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NARMS</t>
+          <t>LENGTH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Planned Number of Arms</t>
+          <t>Trial Length</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>P24W</t>
         </is>
       </c>
     </row>
@@ -1100,17 +1100,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NCOHORT</t>
+          <t>NARMS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Number of Groups/Cohorts</t>
+          <t>Planned Number of Arms</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OBJPRIM</t>
+          <t>NCOHORT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trial Primary Objective</t>
+          <t>Number of Groups/Cohorts</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evaluate efficacy</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OBJSEC</t>
+          <t>OBJPRIM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trial Secondary Objective</t>
+          <t>Trial Primary Objective</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Evaluate safety</t>
+          <t>Evaluate efficacy</t>
         </is>
       </c>
     </row>
@@ -1190,17 +1190,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ONGOSIND</t>
+          <t>OBJSEC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ongoing Study Indicator</t>
+          <t>Trial Secondary Objective</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Evaluate safety</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OUTMSPRI</t>
+          <t>ONGOSIND</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Primary Outcome Measure</t>
+          <t>Ongoing Study Indicator</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ADAS-Cog change from baseline</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PDPSTIND</t>
+          <t>OUTMSPRI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Pediatric Postmarket Study Indicator</t>
+          <t>Primary Outcome Measure</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>ADAS-Cog change from baseline</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PDSTIND</t>
+          <t>PDPSTIND</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pediatric Study Indicator</t>
+          <t>Pediatric Postmarket Study Indicator</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PIPIND</t>
+          <t>PDSTIND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pediatric Investigation Plan Indicator</t>
+          <t>Pediatric Study Indicator</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PLANSUB</t>
+          <t>PIPIND</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Planned Number of Subjects</t>
+          <t>Pediatric Investigation Plan Indicator</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDIND</t>
+          <t>PLANSUB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rare Disease Indicator</t>
+          <t>Planned Number of Subjects</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>300</t>
         </is>
       </c>
     </row>
@@ -1400,17 +1400,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>REGID</t>
+          <t>RDIND</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Registry Identifier</t>
+          <t>Rare Disease Indicator</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>NCT00000000</t>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -1430,17 +1430,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SENDTC</t>
+          <t>REGID</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Study End Date</t>
+          <t>Registry Identifier</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>NCT00000000</t>
         </is>
       </c>
     </row>
@@ -1460,17 +1460,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SEXPOP</t>
+          <t>SENDTC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sex of Participants</t>
+          <t>Study End Date</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>2024-12-31</t>
         </is>
       </c>
     </row>
@@ -1490,17 +1490,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SPONSOR</t>
+          <t>SEXPOP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Clinical Study Sponsor</t>
+          <t>Sex of Participants</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CDISC</t>
+          <t>BOTH</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SDTMVER</t>
+          <t>SPONSOR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SDTM Version</t>
+          <t>Clinical Study Sponsor</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>CDISC</t>
         </is>
       </c>
     </row>
@@ -1550,17 +1550,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SDTIGVER</t>
+          <t>SDTMVER</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SDTM IG Version</t>
+          <t>SDTM Version</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.0</t>
         </is>
       </c>
     </row>
@@ -1580,17 +1580,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>STYPE</t>
+          <t>SDTIGVER</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Study Type</t>
+          <t>SDTM IG Version</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INTERVENTIONAL</t>
+          <t>3.4</t>
         </is>
       </c>
     </row>
@@ -1610,17 +1610,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>STOPRULE</t>
+          <t>STYPE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Study Stop Rules</t>
+          <t>Study Type</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>INTERVENTIONAL</t>
         </is>
       </c>
     </row>
@@ -1640,17 +1640,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SSTDTC</t>
+          <t>STOPRULE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Study Start Date</t>
+          <t>Study Stop Rules</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>NONE</t>
         </is>
       </c>
     </row>
@@ -1670,17 +1670,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>TBLIND</t>
+          <t>SSTDTC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trial Blinding Schema</t>
+          <t>Study Start Date</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DOUBLE BLIND</t>
+          <t>2024-01-01</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TCNTRL</t>
+          <t>TBLIND</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Control Type</t>
+          <t>Trial Blinding Schema</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>PLACEBO</t>
+          <t>DOUBLE BLIND</t>
         </is>
       </c>
     </row>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>THERAREA</t>
+          <t>TCNTRL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Therapeutic Area</t>
+          <t>Control Type</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>NEUROLOGY</t>
+          <t>PLACEBO</t>
         </is>
       </c>
     </row>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TITLE</t>
+          <t>THERAREA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trial Title</t>
+          <t>Therapeutic Area</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Safety and Efficacy Pilot Study</t>
+          <t>NEUROLOGY</t>
         </is>
       </c>
     </row>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TPHASE</t>
+          <t>TITLE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trial Phase Classification</t>
+          <t>Trial Title</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>PHASE II TRIAL</t>
+          <t>Safety and Efficacy Pilot Study</t>
         </is>
       </c>
     </row>
@@ -1820,17 +1820,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TTYPE</t>
+          <t>TPHASE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trial Type</t>
+          <t>Trial Phase Classification</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>EFFICACY</t>
+          <t>PHASE II TRIAL</t>
         </is>
       </c>
     </row>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>INDIC</t>
+          <t>TTYPE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trial Disease/Condition Indication</t>
+          <t>Trial Type</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alzheimer's Disease</t>
+          <t>EFFICACY</t>
         </is>
       </c>
     </row>
@@ -1876,21 +1876,21 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FCNTRY</t>
+          <t>INDIC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Planned Country of Investigational Sites</t>
+          <t>Trial Disease/Condition Indication</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>Alzheimer's Disease</t>
         </is>
       </c>
     </row>
@@ -1910,17 +1910,47 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RANDQT</t>
+          <t>SPREFID</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Randomization Quotient</t>
+          <t>Sponsor's Study Reference ID</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>FCNTRY</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Planned Country of Investigational Sites</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>CAN</t>
         </is>
       </c>
     </row>
